--- a/artfynd/A 28299-2024 artfynd.xlsx
+++ b/artfynd/A 28299-2024 artfynd.xlsx
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118355045</v>
+        <v>118355231</v>
       </c>
       <c r="B7" t="n">
-        <v>58141</v>
+        <v>58133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503068</v>
+        <v>503072</v>
       </c>
       <c r="R7" t="n">
         <v>6561292</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355231</v>
+        <v>118355045</v>
       </c>
       <c r="B8" t="n">
-        <v>58133</v>
+        <v>58141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503072</v>
+        <v>503068</v>
       </c>
       <c r="R8" t="n">
         <v>6561292</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28299-2024 artfynd.xlsx
+++ b/artfynd/A 28299-2024 artfynd.xlsx
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118355231</v>
+        <v>118355045</v>
       </c>
       <c r="B7" t="n">
-        <v>58133</v>
+        <v>58141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503072</v>
+        <v>503068</v>
       </c>
       <c r="R7" t="n">
         <v>6561292</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355045</v>
+        <v>118355231</v>
       </c>
       <c r="B8" t="n">
-        <v>58141</v>
+        <v>58133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503068</v>
+        <v>503072</v>
       </c>
       <c r="R8" t="n">
         <v>6561292</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28299-2024 artfynd.xlsx
+++ b/artfynd/A 28299-2024 artfynd.xlsx
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118355223</v>
+        <v>118355231</v>
       </c>
       <c r="B6" t="n">
-        <v>58105</v>
+        <v>58133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,41 +1112,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1155,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503086</v>
+        <v>503072</v>
       </c>
       <c r="R6" t="n">
-        <v>6561301</v>
+        <v>6561292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1181,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355231</v>
+        <v>118355223</v>
       </c>
       <c r="B8" t="n">
-        <v>58133</v>
+        <v>58105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,27 +1336,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503072</v>
+        <v>503086</v>
       </c>
       <c r="R8" t="n">
-        <v>6561292</v>
+        <v>6561301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28299-2024 artfynd.xlsx
+++ b/artfynd/A 28299-2024 artfynd.xlsx
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118355045</v>
+        <v>118355223</v>
       </c>
       <c r="B7" t="n">
-        <v>58141</v>
+        <v>58105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1241,10 +1241,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503068</v>
+        <v>503086</v>
       </c>
       <c r="R7" t="n">
-        <v>6561292</v>
+        <v>6561301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1307,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355223</v>
+        <v>118355045</v>
       </c>
       <c r="B8" t="n">
-        <v>58105</v>
+        <v>58141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,16 +1350,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,24 +1367,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503086</v>
+        <v>503068</v>
       </c>
       <c r="R8" t="n">
-        <v>6561301</v>
+        <v>6561292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD8" t="b">
